--- a/Longtan_lithic_tools.xlsx
+++ b/Longtan_lithic_tools.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Quina_valleys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1E2244-43DA-4F63-94EC-38B5A63CF19A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4EFE75-1D4A-4E5A-B263-A212765010C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{A79940E2-B962-427A-BDAE-26C815DD4F97}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A79940E2-B962-427A-BDAE-26C815DD4F97}"/>
   </bookViews>
   <sheets>
     <sheet name="Quina scraper" sheetId="9" r:id="rId1"/>
@@ -1765,49 +1765,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A48D0B-1131-4E53-848A-7A8BD61A3B7D}">
   <dimension ref="A1:BA54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.109375" style="3" customWidth="1"/>
-    <col min="2" max="4" width="9.109375" style="3"/>
-    <col min="5" max="5" width="11.109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13.77734375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="28.109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="6.77734375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" style="3" customWidth="1"/>
-    <col min="12" max="13" width="9.109375" style="3"/>
-    <col min="14" max="14" width="10.21875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="3"/>
-    <col min="16" max="16" width="11.109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="13.44140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="14.33203125" style="3" customWidth="1"/>
-    <col min="19" max="19" width="13.77734375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="9.44140625" style="3" customWidth="1"/>
-    <col min="21" max="21" width="12.77734375" style="3" customWidth="1"/>
-    <col min="22" max="22" width="8.5546875" style="3" customWidth="1"/>
-    <col min="23" max="24" width="9.77734375" style="3" customWidth="1"/>
-    <col min="25" max="25" width="9.33203125" style="3" customWidth="1"/>
-    <col min="26" max="26" width="9.77734375" style="3" customWidth="1"/>
-    <col min="27" max="27" width="9.109375" style="3"/>
+    <col min="1" max="1" width="22.125" style="3" customWidth="1"/>
+    <col min="2" max="4" width="9.125" style="3"/>
+    <col min="5" max="5" width="11.125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.75" style="3" customWidth="1"/>
+    <col min="8" max="8" width="28.125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="6.75" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.375" style="3" customWidth="1"/>
+    <col min="12" max="13" width="9.125" style="3"/>
+    <col min="14" max="14" width="10.25" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9.125" style="3"/>
+    <col min="16" max="16" width="11.125" style="3" customWidth="1"/>
+    <col min="17" max="17" width="13.5" style="3" customWidth="1"/>
+    <col min="18" max="18" width="14.375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="13.75" style="3" customWidth="1"/>
+    <col min="20" max="20" width="9.5" style="3" customWidth="1"/>
+    <col min="21" max="21" width="12.75" style="3" customWidth="1"/>
+    <col min="22" max="22" width="8.5" style="3" customWidth="1"/>
+    <col min="23" max="24" width="9.75" style="3" customWidth="1"/>
+    <col min="25" max="25" width="9.375" style="3" customWidth="1"/>
+    <col min="26" max="26" width="9.75" style="3" customWidth="1"/>
+    <col min="27" max="27" width="9.125" style="3"/>
     <col min="28" max="28" width="13" style="3" customWidth="1"/>
-    <col min="29" max="29" width="11.77734375" style="3" customWidth="1"/>
-    <col min="30" max="33" width="9.109375" style="3"/>
-    <col min="34" max="34" width="9.77734375" style="3" customWidth="1"/>
-    <col min="35" max="35" width="9.109375" style="3"/>
-    <col min="36" max="36" width="12.33203125" style="3" customWidth="1"/>
-    <col min="37" max="37" width="11.77734375" style="3" customWidth="1"/>
-    <col min="38" max="43" width="9.109375" style="3"/>
-    <col min="44" max="44" width="12.5546875" style="3" customWidth="1"/>
-    <col min="45" max="45" width="7.5546875" style="3" customWidth="1"/>
-    <col min="46" max="47" width="9.5546875" style="3" customWidth="1"/>
-    <col min="48" max="50" width="9.109375" style="3"/>
-    <col min="51" max="52" width="10.21875" style="3" customWidth="1"/>
-    <col min="53" max="53" width="18.109375" style="3" customWidth="1"/>
-    <col min="54" max="16384" width="9.109375" style="3"/>
+    <col min="29" max="29" width="11.75" style="3" customWidth="1"/>
+    <col min="30" max="33" width="9.125" style="3"/>
+    <col min="34" max="34" width="9.75" style="3" customWidth="1"/>
+    <col min="35" max="35" width="9.125" style="3"/>
+    <col min="36" max="36" width="12.375" style="3" customWidth="1"/>
+    <col min="37" max="37" width="11.75" style="3" customWidth="1"/>
+    <col min="38" max="43" width="9.125" style="3"/>
+    <col min="44" max="44" width="12.5" style="3" customWidth="1"/>
+    <col min="45" max="45" width="7.5" style="3" customWidth="1"/>
+    <col min="46" max="47" width="9.5" style="3" customWidth="1"/>
+    <col min="48" max="50" width="9.125" style="3"/>
+    <col min="51" max="52" width="10.25" style="3" customWidth="1"/>
+    <col min="53" max="53" width="18.125" style="3" customWidth="1"/>
+    <col min="54" max="16384" width="9.125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="2" customFormat="1" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" s="2" customFormat="1" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>374</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>300</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>301</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>0.12786712364882677</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>302</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>0.74467178175618065</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>303</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>0.67551226066509906</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>299</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>0.94053142134120626</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>304</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>0.67417932386085255</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>305</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>0.73914988814317661</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>306</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>0.60995567678145224</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>307</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>0.71778100775193798</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>308</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>0.4876122082585278</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>309</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>0.29202736243113991</v>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>310</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>0.52478134110787178</v>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>311</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>9.7416744475567987E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>312</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>8.7413554633471696E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>313</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>0.16343490304709141</v>
       </c>
     </row>
-    <row r="17" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>314</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>0.79319999999999991</v>
       </c>
     </row>
-    <row r="18" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>315</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>0.66225165562913901</v>
       </c>
     </row>
-    <row r="19" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>316</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>0.31956257594167697</v>
       </c>
     </row>
-    <row r="20" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>317</v>
       </c>
@@ -4085,7 +4085,7 @@
         <v>7.24017127286882E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>318</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>0.7455357142857143</v>
       </c>
     </row>
-    <row r="22" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>319</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>0.20883534136546186</v>
       </c>
     </row>
-    <row r="23" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>320</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>0.74186046511627901</v>
       </c>
     </row>
-    <row r="24" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>321</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>0.20953343439447533</v>
       </c>
     </row>
-    <row r="25" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>322</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>0.26470588235294118</v>
       </c>
     </row>
-    <row r="26" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>323</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>0.44469149527515289</v>
       </c>
     </row>
-    <row r="27" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>324</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>0.34740706746213862</v>
       </c>
     </row>
-    <row r="28" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>298</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>0.69604221635883901</v>
       </c>
     </row>
-    <row r="29" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>325</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>0.88254223652453745</v>
       </c>
     </row>
-    <row r="30" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>326</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>0.95771144278606968</v>
       </c>
     </row>
-    <row r="31" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>327</v>
       </c>
@@ -5370,7 +5370,7 @@
         <v>0.94095711622125544</v>
       </c>
     </row>
-    <row r="32" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>297</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>0.82287822878228789</v>
       </c>
     </row>
-    <row r="33" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>328</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>0.31461761858664089</v>
       </c>
     </row>
-    <row r="34" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>329</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>0.59193488716241216</v>
       </c>
     </row>
-    <row r="35" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>330</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>0.94020418084589208</v>
       </c>
     </row>
-    <row r="36" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>331</v>
       </c>
@@ -5921,7 +5921,7 @@
         <v>0.12504341785342132</v>
       </c>
     </row>
-    <row r="37" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>332</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>0.15662650602409636</v>
       </c>
     </row>
-    <row r="38" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>296</v>
       </c>
@@ -6117,7 +6117,7 @@
         <v>0.28921337729627883</v>
       </c>
     </row>
-    <row r="39" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>333</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>0.97330237957051646</v>
       </c>
     </row>
-    <row r="40" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>334</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>0.2787072638470332</v>
       </c>
     </row>
-    <row r="41" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>335</v>
       </c>
@@ -6423,7 +6423,7 @@
         <v>0.65927977839335172</v>
       </c>
     </row>
-    <row r="42" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>336</v>
       </c>
@@ -6521,7 +6521,7 @@
         <v>0.42982885085574568</v>
       </c>
     </row>
-    <row r="43" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>337</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>0.84266352386564536</v>
       </c>
     </row>
-    <row r="44" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>338</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>0.22308903521328372</v>
       </c>
     </row>
-    <row r="45" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>339</v>
       </c>
@@ -6876,7 +6876,7 @@
         <v>0.8633975481611208</v>
       </c>
     </row>
-    <row r="46" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>340</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>0.4103367267032107</v>
       </c>
     </row>
-    <row r="47" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>341</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>343</v>
       </c>
@@ -7182,7 +7182,7 @@
         <v>0.6226277372262774</v>
       </c>
     </row>
-    <row r="49" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>342</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>0.43918599148130621</v>
       </c>
     </row>
-    <row r="50" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>344</v>
       </c>
@@ -7378,7 +7378,7 @@
         <v>0.45687645687645695</v>
       </c>
     </row>
-    <row r="51" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>295</v>
       </c>
@@ -7502,7 +7502,7 @@
         <v>0.89304306672976819</v>
       </c>
     </row>
-    <row r="52" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>294</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>0.42833726724364013</v>
       </c>
     </row>
-    <row r="53" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>345</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>0.50217994451050341</v>
       </c>
     </row>
-    <row r="54" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>346</v>
       </c>
@@ -7812,40 +7812,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EB59032-A9D7-4FE5-90C5-6EAF8BF85C24}">
   <dimension ref="A1:AG80"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.109375" style="3" customWidth="1"/>
-    <col min="2" max="4" width="9.109375" style="3"/>
-    <col min="5" max="5" width="11.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" style="3" customWidth="1"/>
-    <col min="10" max="11" width="9.109375" style="3"/>
-    <col min="12" max="12" width="10.21875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" style="3"/>
-    <col min="14" max="14" width="10.21875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="11.77734375" style="3" customWidth="1"/>
-    <col min="16" max="16" width="10.21875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="10.109375" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9.5546875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="9.109375" style="3"/>
-    <col min="20" max="20" width="12.77734375" style="3" customWidth="1"/>
-    <col min="21" max="21" width="11.21875" style="3" customWidth="1"/>
-    <col min="22" max="22" width="10.21875" style="3" customWidth="1"/>
-    <col min="23" max="23" width="9.109375" style="3"/>
-    <col min="24" max="24" width="9.77734375" style="3" customWidth="1"/>
-    <col min="25" max="25" width="9.109375" style="3"/>
-    <col min="26" max="26" width="12.33203125" style="3" customWidth="1"/>
-    <col min="27" max="27" width="8.44140625" style="3" customWidth="1"/>
-    <col min="28" max="29" width="12.33203125" style="3" customWidth="1"/>
-    <col min="30" max="30" width="10.109375" style="3" customWidth="1"/>
-    <col min="31" max="31" width="9.109375" style="3"/>
-    <col min="32" max="32" width="10.33203125" style="3" customWidth="1"/>
-    <col min="33" max="16384" width="9.109375" style="3"/>
+    <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
+    <col min="2" max="4" width="9.125" style="3"/>
+    <col min="5" max="5" width="11.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.75" style="3" customWidth="1"/>
+    <col min="9" max="9" width="10.5" style="3" customWidth="1"/>
+    <col min="10" max="11" width="9.125" style="3"/>
+    <col min="12" max="12" width="10.25" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.125" style="3"/>
+    <col min="14" max="14" width="10.25" style="3" customWidth="1"/>
+    <col min="15" max="15" width="11.75" style="3" customWidth="1"/>
+    <col min="16" max="16" width="10.25" style="3" customWidth="1"/>
+    <col min="17" max="17" width="10.125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.5" style="3" customWidth="1"/>
+    <col min="19" max="19" width="9.125" style="3"/>
+    <col min="20" max="20" width="12.75" style="3" customWidth="1"/>
+    <col min="21" max="21" width="11.25" style="3" customWidth="1"/>
+    <col min="22" max="22" width="10.25" style="3" customWidth="1"/>
+    <col min="23" max="23" width="9.125" style="3"/>
+    <col min="24" max="24" width="9.75" style="3" customWidth="1"/>
+    <col min="25" max="25" width="9.125" style="3"/>
+    <col min="26" max="26" width="12.375" style="3" customWidth="1"/>
+    <col min="27" max="27" width="8.5" style="3" customWidth="1"/>
+    <col min="28" max="29" width="12.375" style="3" customWidth="1"/>
+    <col min="30" max="30" width="10.125" style="3" customWidth="1"/>
+    <col min="31" max="31" width="9.125" style="3"/>
+    <col min="32" max="32" width="10.375" style="3" customWidth="1"/>
+    <col min="33" max="16384" width="9.125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="2" customFormat="1" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" s="2" customFormat="1" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>374</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>246</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>0.59583551141313817</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>0.24842685975346951</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>373</v>
       </c>
@@ -8215,7 +8215,7 @@
         <v>0.33786145535430573</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>44</v>
       </c>
@@ -8298,7 +8298,7 @@
         <v>0.30793569351804345</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>0.35719433101128995</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -8464,7 +8464,7 @@
         <v>0.42975305682090625</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -8567,7 +8567,7 @@
         <v>0.68905928130006855</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
@@ -8650,7 +8650,7 @@
         <v>0.32035226630039587</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>215</v>
       </c>
@@ -8733,7 +8733,7 @@
         <v>0.25028089887640448</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -8816,7 +8816,7 @@
         <v>0.43293430106513336</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>0.3773808582944756</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
@@ -8982,7 +8982,7 @@
         <v>0.14617379243803894</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>216</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>0.25348912690684844</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>0.21281424581005584</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>9</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>0.25374017411884031</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>0</v>
       </c>
@@ -9314,7 +9314,7 @@
         <v>0.15241681585283046</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>28</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>0.19542795566502466</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
@@ -9480,7 +9480,7 @@
         <v>0.23144758735440929</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>6</v>
       </c>
@@ -9563,7 +9563,7 @@
         <v>0.37199619319533667</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>3</v>
       </c>
@@ -9646,7 +9646,7 @@
         <v>0.20069775982372384</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>18</v>
       </c>
@@ -9749,7 +9749,7 @@
         <v>0.36168495803744344</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>11</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>0.25078827962777822</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>293</v>
       </c>
@@ -9915,7 +9915,7 @@
         <v>0.26499469214437366</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>217</v>
       </c>
@@ -9998,7 +9998,7 @@
         <v>0.3812025033527045</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>47</v>
       </c>
@@ -10081,7 +10081,7 @@
         <v>0.29821793748174114</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>48</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>0.32186897880539495</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>49</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>0.61016673444489644</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>50</v>
       </c>
@@ -10370,7 +10370,7 @@
         <v>0.39652292742180384</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>51</v>
       </c>
@@ -10453,7 +10453,7 @@
         <v>0.29274584666185122</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>52</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>0.32201027785036146</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>53</v>
       </c>
@@ -10639,7 +10639,7 @@
         <v>0.23785828025477704</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>54</v>
       </c>
@@ -10722,7 +10722,7 @@
         <v>0.31602112676056338</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>55</v>
       </c>
@@ -10805,7 +10805,7 @@
         <v>0.32681980906921237</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>56</v>
       </c>
@@ -10888,7 +10888,7 @@
         <v>0.24696123521681995</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>57</v>
       </c>
@@ -10971,7 +10971,7 @@
         <v>0.23064463880790412</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>58</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>0.30942281472504174</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>59</v>
       </c>
@@ -11137,7 +11137,7 @@
         <v>0.422892455266556</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>218</v>
       </c>
@@ -11240,7 +11240,7 @@
         <v>0.51759530791788866</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>60</v>
       </c>
@@ -11343,7 +11343,7 @@
         <v>0.54426891991182957</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>61</v>
       </c>
@@ -11426,7 +11426,7 @@
         <v>0.25423565652676161</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>62</v>
       </c>
@@ -11529,7 +11529,7 @@
         <v>0.60067141570457727</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>63</v>
       </c>
@@ -11611,7 +11611,7 @@
         <v>0.20132864400156308</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>64</v>
       </c>
@@ -11693,7 +11693,7 @@
         <v>0.19076801423346842</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>219</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>0.21866338158299969</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>220</v>
       </c>
@@ -11857,7 +11857,7 @@
         <v>0.18281642917015928</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>65</v>
       </c>
@@ -11939,7 +11939,7 @@
         <v>0.56413388712435864</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>66</v>
       </c>
@@ -12021,7 +12021,7 @@
         <v>0.24435553015147191</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>67</v>
       </c>
@@ -12103,7 +12103,7 @@
         <v>0.24851662757002901</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>68</v>
       </c>
@@ -12185,7 +12185,7 @@
         <v>0.25397584598828166</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>69</v>
       </c>
@@ -12267,7 +12267,7 @@
         <v>0.19689869643009286</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>70</v>
       </c>
@@ -12349,7 +12349,7 @@
         <v>0.16195924204504827</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>71</v>
       </c>
@@ -12431,7 +12431,7 @@
         <v>0.13273224447564852</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>72</v>
       </c>
@@ -12513,7 +12513,7 @@
         <v>0.20240431795878311</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>73</v>
       </c>
@@ -12595,7 +12595,7 @@
         <v>0.44680591181140827</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>74</v>
       </c>
@@ -12677,7 +12677,7 @@
         <v>0.23682034318792641</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>75</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>0.47754314503162182</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>76</v>
       </c>
@@ -12841,7 +12841,7 @@
         <v>0.29494680851063826</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>77</v>
       </c>
@@ -12923,7 +12923,7 @@
         <v>0.1943934835253541</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>78</v>
       </c>
@@ -13005,7 +13005,7 @@
         <v>0.17292509146928556</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>79</v>
       </c>
@@ -13087,7 +13087,7 @@
         <v>0.41076936635233985</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>80</v>
       </c>
@@ -13169,7 +13169,7 @@
         <v>0.40288647950025136</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>81</v>
       </c>
@@ -13251,7 +13251,7 @@
         <v>0.23237855795995332</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>82</v>
       </c>
@@ -13333,7 +13333,7 @@
         <v>0.42502962355300328</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>83</v>
       </c>
@@ -13415,7 +13415,7 @@
         <v>0.26682097533721766</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>84</v>
       </c>
@@ -13497,7 +13497,7 @@
         <v>0.3083718973496003</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>85</v>
       </c>
@@ -13579,7 +13579,7 @@
         <v>0.25518594655204629</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>86</v>
       </c>
@@ -13661,7 +13661,7 @@
         <v>0.20449919657204069</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>87</v>
       </c>
@@ -13743,7 +13743,7 @@
         <v>0.31642172523961665</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>88</v>
       </c>
@@ -13825,7 +13825,7 @@
         <v>0.28778280542986417</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>89</v>
       </c>
@@ -13907,7 +13907,7 @@
         <v>0.29203794193733829</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>90</v>
       </c>
@@ -13989,7 +13989,7 @@
         <v>0.19774569903104608</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>91</v>
       </c>
@@ -14071,7 +14071,7 @@
         <v>0.27711561382598326</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>92</v>
       </c>
@@ -14153,7 +14153,7 @@
         <v>0.32178393745557921</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>93</v>
       </c>
@@ -14235,7 +14235,7 @@
         <v>0.27785655645943724</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>94</v>
       </c>
@@ -14317,7 +14317,7 @@
         <v>0.21663334666133544</v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>221</v>
       </c>
@@ -14399,7 +14399,7 @@
         <v>0.31054390762686113</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
         <v>222</v>
       </c>
@@ -14481,7 +14481,7 @@
         <v>0.30724860603730053</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>119</v>
       </c>
@@ -14563,7 +14563,7 @@
         <v>0.38806106591096085</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>223</v>
       </c>
@@ -14654,19 +14654,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4AC8C99-BC3C-46BA-87FA-7A3B58F7A3A6}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" style="3" customWidth="1"/>
-    <col min="2" max="4" width="9.109375" style="3"/>
+    <col min="1" max="1" width="20.75" style="3" customWidth="1"/>
+    <col min="2" max="4" width="9.125" style="3"/>
     <col min="5" max="5" width="11" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" style="3" customWidth="1"/>
-    <col min="8" max="10" width="9.109375" style="3"/>
-    <col min="11" max="11" width="9.5546875" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="3"/>
+    <col min="6" max="6" width="12.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.75" style="3" customWidth="1"/>
+    <col min="8" max="10" width="9.125" style="3"/>
+    <col min="11" max="11" width="9.5" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="2" customFormat="1" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -14707,7 +14707,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -14748,7 +14748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>29</v>
       </c>
@@ -14789,7 +14789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
@@ -14830,7 +14830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>26</v>
       </c>
@@ -14871,7 +14871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
@@ -14912,7 +14912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
@@ -14953,7 +14953,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
@@ -14994,7 +14994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>31</v>
       </c>
@@ -15035,7 +15035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
@@ -15076,7 +15076,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
@@ -15117,7 +15117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>32</v>
       </c>
@@ -15158,7 +15158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>168</v>
       </c>
@@ -15199,7 +15199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>155</v>
       </c>
@@ -15240,7 +15240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
@@ -15281,7 +15281,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>43</v>
       </c>
@@ -15322,7 +15322,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
@@ -15363,7 +15363,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>249</v>
       </c>
@@ -15404,7 +15404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>2</v>
       </c>
@@ -15445,7 +15445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
@@ -15486,7 +15486,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -15527,7 +15527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
@@ -15568,7 +15568,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>19</v>
       </c>
@@ -15609,7 +15609,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>42</v>
       </c>
@@ -15650,7 +15650,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
@@ -15691,7 +15691,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>13</v>
       </c>
@@ -15732,7 +15732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>24</v>
       </c>
@@ -15773,7 +15773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>138</v>
       </c>
@@ -15814,7 +15814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>104</v>
       </c>
@@ -15855,7 +15855,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>147</v>
       </c>
@@ -15905,20 +15905,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9285E22C-273E-47A6-A4BA-103D4DA32B78}">
   <dimension ref="A1:M82"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="4" width="9.109375" style="3"/>
-    <col min="5" max="5" width="11.21875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="18.21875" style="3" customWidth="1"/>
-    <col min="8" max="10" width="9.109375" style="3"/>
-    <col min="11" max="11" width="10.21875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" style="3"/>
-    <col min="14" max="16384" width="9.109375" style="3"/>
+    <col min="2" max="4" width="9.125" style="3"/>
+    <col min="5" max="5" width="11.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.25" style="3" customWidth="1"/>
+    <col min="8" max="10" width="9.125" style="3"/>
+    <col min="11" max="11" width="10.25" style="3" customWidth="1"/>
+    <col min="12" max="12" width="9.125" style="3"/>
+    <col min="14" max="16384" width="9.125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -15956,7 +15956,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>95</v>
       </c>
@@ -15994,7 +15994,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>96</v>
       </c>
@@ -16032,7 +16032,7 @@
         <v>39.799999999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>97</v>
       </c>
@@ -16070,7 +16070,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>358</v>
       </c>
@@ -16108,7 +16108,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>98</v>
       </c>
@@ -16146,7 +16146,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>99</v>
       </c>
@@ -16184,7 +16184,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>359</v>
       </c>
@@ -16222,7 +16222,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>100</v>
       </c>
@@ -16260,7 +16260,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>101</v>
       </c>
@@ -16298,7 +16298,7 @@
         <v>85.7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>102</v>
       </c>
@@ -16336,7 +16336,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>103</v>
       </c>
@@ -16374,7 +16374,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>360</v>
       </c>
@@ -16412,7 +16412,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>105</v>
       </c>
@@ -16450,7 +16450,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>106</v>
       </c>
@@ -16488,7 +16488,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>107</v>
       </c>
@@ -16526,7 +16526,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>108</v>
       </c>
@@ -16564,7 +16564,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>109</v>
       </c>
@@ -16602,7 +16602,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>361</v>
       </c>
@@ -16640,7 +16640,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>362</v>
       </c>
@@ -16678,7 +16678,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>363</v>
       </c>
@@ -16716,7 +16716,7 @@
         <v>85.6</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>110</v>
       </c>
@@ -16754,7 +16754,7 @@
         <v>42.7</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>364</v>
       </c>
@@ -16792,7 +16792,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>111</v>
       </c>
@@ -16830,7 +16830,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>112</v>
       </c>
@@ -16868,7 +16868,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>113</v>
       </c>
@@ -16906,7 +16906,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>114</v>
       </c>
@@ -16944,7 +16944,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>115</v>
       </c>
@@ -16982,7 +16982,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>116</v>
       </c>
@@ -17020,7 +17020,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>117</v>
       </c>
@@ -17058,7 +17058,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>118</v>
       </c>
@@ -17096,7 +17096,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>120</v>
       </c>
@@ -17134,7 +17134,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>121</v>
       </c>
@@ -17172,7 +17172,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>365</v>
       </c>
@@ -17210,7 +17210,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>122</v>
       </c>
@@ -17248,7 +17248,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>123</v>
       </c>
@@ -17286,7 +17286,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>124</v>
       </c>
@@ -17324,7 +17324,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>125</v>
       </c>
@@ -17362,7 +17362,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>126</v>
       </c>
@@ -17400,7 +17400,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>366</v>
       </c>
@@ -17438,7 +17438,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>127</v>
       </c>
@@ -17476,7 +17476,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>128</v>
       </c>
@@ -17514,7 +17514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>129</v>
       </c>
@@ -17552,7 +17552,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>367</v>
       </c>
@@ -17590,7 +17590,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>130</v>
       </c>
@@ -17628,7 +17628,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>131</v>
       </c>
@@ -17666,7 +17666,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>132</v>
       </c>
@@ -17704,7 +17704,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>368</v>
       </c>
@@ -17742,7 +17742,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>133</v>
       </c>
@@ -17780,7 +17780,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>134</v>
       </c>
@@ -17818,7 +17818,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>135</v>
       </c>
@@ -17856,7 +17856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>136</v>
       </c>
@@ -17894,7 +17894,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>137</v>
       </c>
@@ -17932,7 +17932,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>369</v>
       </c>
@@ -17970,7 +17970,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>370</v>
       </c>
@@ -18008,7 +18008,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>139</v>
       </c>
@@ -18046,7 +18046,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>140</v>
       </c>
@@ -18084,7 +18084,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>141</v>
       </c>
@@ -18122,7 +18122,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>142</v>
       </c>
@@ -18160,7 +18160,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>371</v>
       </c>
@@ -18198,7 +18198,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>143</v>
       </c>
@@ -18236,7 +18236,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>144</v>
       </c>
@@ -18274,7 +18274,7 @@
         <v>57.1</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>145</v>
       </c>
@@ -18312,7 +18312,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>146</v>
       </c>
@@ -18350,7 +18350,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>148</v>
       </c>
@@ -18388,7 +18388,7 @@
         <v>42.1</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>149</v>
       </c>
@@ -18426,7 +18426,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>150</v>
       </c>
@@ -18464,7 +18464,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>151</v>
       </c>
@@ -18502,7 +18502,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>152</v>
       </c>
@@ -18540,7 +18540,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>153</v>
       </c>
@@ -18578,7 +18578,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>154</v>
       </c>
@@ -18616,7 +18616,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>156</v>
       </c>
@@ -18654,7 +18654,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>157</v>
       </c>
@@ -18692,7 +18692,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>158</v>
       </c>
@@ -18730,7 +18730,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>372</v>
       </c>
@@ -18768,7 +18768,7 @@
         <v>109.2</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>159</v>
       </c>
@@ -18806,7 +18806,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>160</v>
       </c>
@@ -18844,7 +18844,7 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
         <v>161</v>
       </c>
@@ -18882,7 +18882,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>162</v>
       </c>
@@ -18920,7 +18920,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>163</v>
       </c>
@@ -18958,7 +18958,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>164</v>
       </c>
@@ -18996,7 +18996,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>165</v>
       </c>
